--- a/results/pooled_results_OR_multi_exposure_models_warm_parent.xlsx
+++ b/results/pooled_results_OR_multi_exposure_models_warm_parent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Keiji\Documents\Research\ahs_fibromyalgia\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2785D838-C58C-4E7B-8AC9-842E15C9A190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FE5CC2-A01B-4CED-9A39-0EAD3488E3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{797B858C-DA94-466A-A931-46BE830858D9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="46">
   <si>
     <t>Depression</t>
   </si>
@@ -182,6 +182,12 @@
   </si>
   <si>
     <t>Stomach ulcer</t>
+  </si>
+  <si>
+    <t>Rheumatism</t>
+  </si>
+  <si>
+    <t>&lt;.0001</t>
   </si>
 </sst>
 </file>
@@ -302,7 +308,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -320,11 +326,11 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -334,11 +340,9 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -674,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9215179F-2EFE-4E44-8C52-C38DCB1662E2}">
-  <dimension ref="B1:V51"/>
+  <dimension ref="B1:V54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" style="3" bestFit="1" customWidth="1"/>
@@ -715,30 +719,30 @@
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20"/>
-      <c r="I5" s="18" t="s">
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="I5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="20"/>
-      <c r="N5" s="18" t="s">
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="18"/>
+      <c r="N5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="20"/>
-      <c r="S5" s="18" t="s">
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="18"/>
+      <c r="S5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="19"/>
-      <c r="U5" s="19"/>
-      <c r="V5" s="20"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="18"/>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
       <c r="D6" s="9"/>
@@ -813,90 +817,89 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="15"/>
+      <c r="E8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="13"/>
       <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="21"/>
-      <c r="L8" s="15"/>
+      <c r="J8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="15"/>
+      <c r="L8" s="13"/>
       <c r="N8" s="1">
         <v>1</v>
       </c>
-      <c r="O8" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="15"/>
+      <c r="O8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="13"/>
       <c r="S8" s="1">
         <v>1</v>
       </c>
-      <c r="T8" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="U8" s="21"/>
-      <c r="V8" s="15"/>
+      <c r="T8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="U8" s="15"/>
+      <c r="V8" s="13"/>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="12">
-        <v>1.5912455000000001</v>
-      </c>
-      <c r="E9" s="12">
-        <v>1.0516992999999999</v>
-      </c>
-      <c r="F9" s="12">
-        <v>2.4075915999999999</v>
-      </c>
-      <c r="G9" s="17">
-        <v>2.7924999999999998E-2</v>
-      </c>
-      <c r="H9" s="3"/>
+      <c r="D9" s="1">
+        <v>1.4713158</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.95908959999999999</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2.2571096000000002</v>
+      </c>
+      <c r="G9" s="13">
+        <v>7.6932E-2</v>
+      </c>
       <c r="I9" s="12">
-        <v>1.6799265999999999</v>
+        <v>1.5396198999999999</v>
       </c>
       <c r="J9" s="12">
-        <v>1.1149856</v>
+        <v>1.0073276</v>
       </c>
       <c r="K9" s="12">
-        <v>2.5311121000000001</v>
-      </c>
-      <c r="L9" s="17">
-        <v>1.3140000000000001E-2</v>
+        <v>2.3531863</v>
+      </c>
+      <c r="L9" s="14">
+        <v>4.6188E-2</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="12">
-        <v>1.7669010999999999</v>
+        <v>1.6320345999999999</v>
       </c>
       <c r="O9" s="12">
-        <v>1.17089</v>
+        <v>1.0660229000000001</v>
       </c>
       <c r="P9" s="12">
-        <v>2.6662962000000001</v>
-      </c>
-      <c r="Q9" s="17">
-        <v>6.7169999999999999E-3</v>
+        <v>2.4985738999999998</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>2.4199999999999999E-2</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="12">
-        <v>1.721417</v>
+        <v>1.5948567</v>
       </c>
       <c r="T9" s="12">
-        <v>1.1434149</v>
+        <v>1.0451254000000001</v>
       </c>
       <c r="U9" s="12">
-        <v>2.5916022000000001</v>
-      </c>
-      <c r="V9" s="17">
-        <v>9.2899999999999996E-3</v>
+        <v>2.4337442999999999</v>
+      </c>
+      <c r="V9" s="14">
+        <v>3.0429000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.3">
@@ -904,68 +907,68 @@
         <v>1</v>
       </c>
       <c r="D10" s="1">
-        <v>1.5490174999999999</v>
+        <v>1.4000419</v>
       </c>
       <c r="E10" s="1">
-        <v>0.8617361</v>
+        <v>0.75085109999999999</v>
       </c>
       <c r="F10" s="1">
-        <v>2.7844435000000001</v>
-      </c>
-      <c r="G10" s="15">
-        <v>0.143509</v>
+        <v>2.6105274000000001</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0.28966999999999998</v>
       </c>
       <c r="I10" s="1">
-        <v>1.6373702000000001</v>
+        <v>1.4608756000000001</v>
       </c>
       <c r="J10" s="1">
-        <v>0.91518820000000001</v>
+        <v>0.78851389999999999</v>
       </c>
       <c r="K10" s="1">
-        <v>2.9294315000000002</v>
-      </c>
-      <c r="L10" s="15">
-        <v>9.6610000000000001E-2</v>
+        <v>2.7065567000000001</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0.22819</v>
       </c>
       <c r="N10" s="1">
-        <v>1.6637687999999999</v>
+        <v>1.4877568999999999</v>
       </c>
       <c r="O10" s="1">
-        <v>0.92862299999999998</v>
+        <v>0.80150480000000002</v>
       </c>
       <c r="P10" s="1">
-        <v>2.9808938</v>
-      </c>
-      <c r="Q10" s="15">
-        <v>8.7041999999999994E-2</v>
+        <v>2.7615810000000001</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>0.20799000000000001</v>
       </c>
       <c r="S10" s="1">
-        <v>1.6986768999999999</v>
+        <v>1.5212467999999999</v>
       </c>
       <c r="T10" s="1">
-        <v>0.95118650000000005</v>
+        <v>0.82133080000000003</v>
       </c>
       <c r="U10" s="1">
-        <v>3.0335830000000001</v>
-      </c>
-      <c r="V10" s="15">
-        <v>7.331E-2</v>
+        <v>2.8176122000000001</v>
+      </c>
+      <c r="V10" s="13">
+        <v>0.182092</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G11" s="15"/>
+      <c r="G11" s="13"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="15"/>
+      <c r="L11" s="13"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="15"/>
+      <c r="Q11" s="13"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
-      <c r="V11" s="15"/>
+      <c r="V11" s="13"/>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
@@ -977,39 +980,39 @@
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="15"/>
+      <c r="G12" s="13"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="15"/>
+      <c r="L12" s="13"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-      <c r="Q12" s="15"/>
+      <c r="Q12" s="13"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
-      <c r="V12" s="15"/>
+      <c r="V12" s="13"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C13" s="7">
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>1.2508927999999999</v>
+        <v>1.1517809999999999</v>
       </c>
       <c r="E13" s="1">
-        <v>0.75141400000000003</v>
+        <v>0.68869519999999995</v>
       </c>
       <c r="F13" s="1">
-        <v>2.0823844</v>
-      </c>
-      <c r="G13" s="15">
-        <v>0.38861299999999999</v>
+        <v>1.9262505999999999</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0.58985299999999996</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.3">
@@ -1017,16 +1020,16 @@
         <v>2</v>
       </c>
       <c r="D14" s="12">
-        <v>1.8977318999999999</v>
+        <v>1.7536551</v>
       </c>
       <c r="E14" s="12">
-        <v>1.1316092</v>
+        <v>1.0321604</v>
       </c>
       <c r="F14" s="12">
-        <v>3.1825351999999998</v>
-      </c>
-      <c r="G14" s="17">
-        <v>1.5181999999999999E-2</v>
+        <v>2.9794849000000001</v>
+      </c>
+      <c r="G14" s="14">
+        <v>3.7810000000000003E-2</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -1034,29 +1037,21 @@
         <v>3</v>
       </c>
       <c r="D15" s="12">
-        <v>3.3149335</v>
+        <v>2.9947035</v>
       </c>
       <c r="E15" s="12">
-        <v>1.7922064</v>
+        <v>1.5766359000000001</v>
       </c>
       <c r="F15" s="12">
-        <v>6.1314276999999997</v>
-      </c>
-      <c r="G15" s="17">
-        <v>1.3899999999999999E-4</v>
+        <v>5.6882181999999997</v>
+      </c>
+      <c r="G15" s="14">
+        <v>8.2399999999999997E-4</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C16" s="7"/>
-      <c r="G16" s="15"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="15"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="15"/>
+      <c r="G16" s="13"/>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
@@ -1065,86 +1060,55 @@
       <c r="C17" s="7">
         <v>0</v>
       </c>
-      <c r="G17" s="15"/>
+      <c r="G17" s="13"/>
       <c r="I17" s="1">
         <v>1</v>
       </c>
-      <c r="J17" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="21"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="15"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="15"/>
+      <c r="J17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="15"/>
+      <c r="L17" s="13"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C18" s="7">
         <v>1</v>
       </c>
-      <c r="G18" s="15"/>
+      <c r="G18" s="13"/>
       <c r="I18" s="1">
-        <v>1.3106351000000001</v>
+        <v>1.4142013</v>
       </c>
       <c r="J18" s="1">
-        <v>0.85361969999999998</v>
+        <v>0.90791619999999995</v>
       </c>
       <c r="K18" s="1">
-        <v>2.0123299000000001</v>
-      </c>
-      <c r="L18" s="15">
-        <v>0.21615000000000001</v>
-      </c>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="15"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="15"/>
+        <v>2.2028082000000002</v>
+      </c>
+      <c r="L18" s="13">
+        <v>0.12528400000000001</v>
+      </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C19" s="7">
         <v>2</v>
       </c>
-      <c r="G19" s="15"/>
-      <c r="I19" s="1">
-        <v>1.6448902000000001</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0.95006299999999999</v>
-      </c>
-      <c r="K19" s="1">
-        <v>2.8478780000000001</v>
-      </c>
-      <c r="L19" s="15">
-        <v>7.5499999999999998E-2</v>
-      </c>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="15"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="15"/>
+      <c r="G19" s="13"/>
+      <c r="I19" s="12">
+        <v>1.7967219999999999</v>
+      </c>
+      <c r="J19" s="12">
+        <v>1.0279465999999999</v>
+      </c>
+      <c r="K19" s="12">
+        <v>3.1404448999999999</v>
+      </c>
+      <c r="L19" s="14">
+        <v>3.9726999999999998E-2</v>
+      </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C20" s="7"/>
-      <c r="G20" s="15"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="15"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="15"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
@@ -1153,97 +1117,73 @@
       <c r="C21" s="7">
         <v>0</v>
       </c>
-      <c r="G21" s="15"/>
+      <c r="G21" s="13"/>
       <c r="N21" s="1">
         <v>1</v>
       </c>
-      <c r="O21" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="15"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="15"/>
+      <c r="O21" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="13"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C22" s="7">
         <v>1</v>
       </c>
-      <c r="G22" s="15"/>
-      <c r="N22" s="12">
-        <v>1.9674096999999999</v>
-      </c>
-      <c r="O22" s="12">
-        <v>1.050681</v>
-      </c>
-      <c r="P22" s="12">
-        <v>3.6839922999999999</v>
-      </c>
-      <c r="Q22" s="17">
-        <v>3.4512000000000001E-2</v>
-      </c>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="15"/>
+      <c r="G22" s="13"/>
+      <c r="N22" s="1">
+        <v>1.8020137000000001</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0.95680500000000002</v>
+      </c>
+      <c r="P22" s="1">
+        <v>3.3938508000000001</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>6.8229999999999999E-2</v>
+      </c>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C23" s="7">
         <v>2</v>
       </c>
-      <c r="G23" s="15"/>
+      <c r="G23" s="13"/>
       <c r="N23" s="12">
-        <v>2.7392229000000001</v>
+        <v>2.5865966999999999</v>
       </c>
       <c r="O23" s="12">
-        <v>1.3883459</v>
+        <v>1.3357996000000001</v>
       </c>
       <c r="P23" s="12">
-        <v>5.4045189000000002</v>
-      </c>
-      <c r="Q23" s="17">
-        <v>3.7260000000000001E-3</v>
-      </c>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="15"/>
+        <v>5.0085977000000002</v>
+      </c>
+      <c r="Q23" s="14">
+        <v>4.8500000000000001E-3</v>
+      </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C24" s="7">
         <v>3</v>
       </c>
-      <c r="G24" s="15"/>
-      <c r="N24" s="12">
-        <v>3.1169972000000001</v>
-      </c>
-      <c r="O24" s="12">
-        <v>1.22184</v>
-      </c>
-      <c r="P24" s="12">
-        <v>7.9516723999999996</v>
-      </c>
-      <c r="Q24" s="17">
-        <v>1.7402000000000001E-2</v>
-      </c>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="15"/>
+      <c r="G24" s="13"/>
+      <c r="N24" s="1">
+        <v>2.5299619</v>
+      </c>
+      <c r="O24" s="1">
+        <v>0.95282</v>
+      </c>
+      <c r="P24" s="1">
+        <v>6.7176457000000003</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>6.2449999999999999E-2</v>
+      </c>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C25" s="7"/>
-      <c r="G25" s="15"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="15"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="15"/>
+      <c r="G25" s="13"/>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
@@ -1252,235 +1192,215 @@
       <c r="C26" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="15"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="15"/>
+      <c r="G26" s="13"/>
       <c r="S26" s="1">
         <v>1</v>
       </c>
-      <c r="T26" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="U26" s="21"/>
-      <c r="V26" s="15"/>
+      <c r="T26" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="U26" s="15"/>
+      <c r="V26" s="13"/>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="15"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="15"/>
+      <c r="G27" s="13"/>
       <c r="S27" s="1">
-        <v>0.89175020000000005</v>
+        <v>0.92445900000000003</v>
       </c>
       <c r="T27" s="1">
-        <v>0.49697550000000001</v>
+        <v>0.50635669999999999</v>
       </c>
       <c r="U27" s="1">
-        <v>1.6001160000000001</v>
-      </c>
-      <c r="V27" s="15">
-        <v>0.70067000000000002</v>
+        <v>1.687791</v>
+      </c>
+      <c r="V27" s="13">
+        <v>0.79793000000000003</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C28" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G28" s="15"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="15"/>
+      <c r="G28" s="13"/>
       <c r="S28" s="1">
-        <v>1.1694247</v>
+        <v>1.1981552</v>
       </c>
       <c r="T28" s="1">
-        <v>0.68711509999999998</v>
+        <v>0.6987911</v>
       </c>
       <c r="U28" s="1">
-        <v>1.9902839999999999</v>
-      </c>
-      <c r="V28" s="15">
-        <v>0.56372</v>
+        <v>2.0543705999999999</v>
+      </c>
+      <c r="V28" s="13">
+        <v>0.51089399999999996</v>
       </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C29" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G29" s="15"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="15"/>
+      <c r="G29" s="13"/>
       <c r="S29" s="1">
-        <v>1.1267668</v>
+        <v>0.95068260000000004</v>
       </c>
       <c r="T29" s="1">
-        <v>0.63255070000000002</v>
+        <v>0.51103149999999997</v>
       </c>
       <c r="U29" s="1">
-        <v>2.0071175000000001</v>
-      </c>
-      <c r="V29" s="15">
-        <v>0.68503999999999998</v>
+        <v>1.7685744000000001</v>
+      </c>
+      <c r="V29" s="13">
+        <v>0.87299599999999999</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G30" s="15"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="15"/>
+      <c r="G30" s="13"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
-      <c r="V30" s="15"/>
+      <c r="V30" s="13"/>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D31" s="12">
-        <v>0.97006919999999996</v>
+        <v>0.96112730000000002</v>
       </c>
       <c r="E31" s="12">
-        <v>0.95130490000000001</v>
+        <v>0.94062840000000003</v>
       </c>
       <c r="F31" s="12">
-        <v>0.98920359999999996</v>
-      </c>
-      <c r="G31" s="17">
-        <v>2.3059999999999999E-3</v>
+        <v>0.98207290000000003</v>
+      </c>
+      <c r="G31" s="14">
+        <v>3.1700000000000001E-4</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="12">
-        <v>0.97192599999999996</v>
+        <v>0.9632039</v>
       </c>
       <c r="J31" s="12">
-        <v>0.95307960000000003</v>
+        <v>0.94252440000000004</v>
       </c>
       <c r="K31" s="12">
-        <v>0.9911451</v>
-      </c>
-      <c r="L31" s="17">
-        <v>4.3800000000000002E-3</v>
+        <v>0.98433709999999996</v>
+      </c>
+      <c r="L31" s="14">
+        <v>7.1699999999999997E-4</v>
       </c>
       <c r="M31" s="3"/>
       <c r="N31" s="12">
-        <v>0.96683909999999995</v>
+        <v>0.95777730000000005</v>
       </c>
       <c r="O31" s="12">
-        <v>0.94828970000000001</v>
+        <v>0.9374209</v>
       </c>
       <c r="P31" s="12">
-        <v>0.98575140000000006</v>
-      </c>
-      <c r="Q31" s="17">
-        <v>6.5099999999999999E-4</v>
+        <v>0.97857570000000005</v>
+      </c>
+      <c r="Q31" s="14">
+        <v>8.4599999999999996E-5</v>
       </c>
       <c r="R31" s="3"/>
       <c r="S31" s="12">
-        <v>0.96974450000000001</v>
+        <v>0.96041299999999996</v>
       </c>
       <c r="T31" s="12">
-        <v>0.95114540000000003</v>
+        <v>0.94002209999999997</v>
       </c>
       <c r="U31" s="12">
-        <v>0.98870729999999996</v>
-      </c>
-      <c r="V31" s="17">
-        <v>1.89E-3</v>
+        <v>0.98124630000000002</v>
+      </c>
+      <c r="V31" s="14">
+        <v>2.2900000000000001E-4</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G32" s="15"/>
+      <c r="G32" s="13"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
-      <c r="L32" s="15"/>
+      <c r="L32" s="13"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-      <c r="Q32" s="15"/>
+      <c r="Q32" s="13"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
-      <c r="V32" s="15"/>
+      <c r="V32" s="13"/>
     </row>
     <row r="33" spans="2:22" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D33" s="1">
-        <v>0.96206849999999999</v>
+        <v>0.95098329999999998</v>
       </c>
       <c r="E33" s="1">
-        <v>0.91366289999999994</v>
+        <v>0.89964189999999999</v>
       </c>
       <c r="F33" s="1">
-        <v>1.0130385</v>
-      </c>
-      <c r="G33" s="15">
-        <v>0.14196500000000001</v>
+        <v>1.0052546</v>
+      </c>
+      <c r="G33" s="13">
+        <v>7.5847999999999999E-2</v>
       </c>
       <c r="I33" s="1">
-        <v>0.96721789999999996</v>
+        <v>0.95567760000000002</v>
       </c>
       <c r="J33" s="1">
-        <v>0.91867589999999999</v>
+        <v>0.90437009999999995</v>
       </c>
       <c r="K33" s="1">
-        <v>1.0183248</v>
-      </c>
-      <c r="L33" s="15">
-        <v>0.20437</v>
+        <v>1.0098959000000001</v>
+      </c>
+      <c r="L33" s="13">
+        <v>0.107209</v>
       </c>
       <c r="N33" s="1">
-        <v>0.96596680000000001</v>
+        <v>0.95511179999999996</v>
       </c>
       <c r="O33" s="1">
-        <v>0.91681279999999998</v>
+        <v>0.90333470000000005</v>
       </c>
       <c r="P33" s="1">
-        <v>1.0177563000000001</v>
-      </c>
-      <c r="Q33" s="15">
-        <v>0.19362399999999999</v>
+        <v>1.0098566</v>
+      </c>
+      <c r="Q33" s="13">
+        <v>0.10614999999999999</v>
       </c>
       <c r="S33" s="1">
-        <v>0.96895929999999997</v>
+        <v>0.95752630000000005</v>
       </c>
       <c r="T33" s="1">
-        <v>0.92029280000000002</v>
+        <v>0.9053928</v>
       </c>
       <c r="U33" s="1">
-        <v>1.0201993</v>
-      </c>
-      <c r="V33" s="15">
-        <v>0.23022999999999999</v>
+        <v>1.0126618000000001</v>
+      </c>
+      <c r="V33" s="13">
+        <v>0.12842000000000001</v>
       </c>
     </row>
     <row r="34" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G34" s="15"/>
+      <c r="G34" s="13"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="15"/>
+      <c r="L34" s="13"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="15"/>
+      <c r="Q34" s="13"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
-      <c r="V34" s="15"/>
+      <c r="V34" s="13"/>
     </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
@@ -1492,87 +1412,87 @@
       <c r="D35" s="1">
         <v>1</v>
       </c>
-      <c r="E35" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F35" s="21"/>
-      <c r="G35" s="15"/>
+      <c r="E35" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="15"/>
+      <c r="G35" s="13"/>
       <c r="I35" s="1">
         <v>1</v>
       </c>
-      <c r="J35" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="K35" s="21"/>
-      <c r="L35" s="15"/>
+      <c r="J35" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K35" s="15"/>
+      <c r="L35" s="13"/>
       <c r="N35" s="1">
         <v>1</v>
       </c>
-      <c r="O35" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="15"/>
+      <c r="O35" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="13"/>
       <c r="S35" s="1">
         <v>1</v>
       </c>
-      <c r="T35" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="U35" s="21"/>
-      <c r="V35" s="15"/>
+      <c r="T35" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="U35" s="15"/>
+      <c r="V35" s="13"/>
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C36" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="1">
-        <v>1.6217233</v>
+        <v>1.573272</v>
       </c>
       <c r="E36" s="1">
-        <v>0.93536640000000004</v>
+        <v>0.8952002</v>
       </c>
       <c r="F36" s="1">
-        <v>2.8117177999999998</v>
-      </c>
-      <c r="G36" s="15">
-        <v>8.5042000000000006E-2</v>
+        <v>2.7649509999999999</v>
+      </c>
+      <c r="G36" s="13">
+        <v>0.115172</v>
       </c>
       <c r="I36" s="1">
-        <v>1.4965679999999999</v>
+        <v>1.4429864999999999</v>
       </c>
       <c r="J36" s="1">
-        <v>0.86785389999999996</v>
+        <v>0.82740040000000004</v>
       </c>
       <c r="K36" s="1">
-        <v>2.5807521000000002</v>
-      </c>
-      <c r="L36" s="15">
-        <v>0.14693000000000001</v>
+        <v>2.5165685</v>
+      </c>
+      <c r="L36" s="13">
+        <v>0.19616</v>
       </c>
       <c r="N36" s="1">
-        <v>1.5958241</v>
+        <v>1.5309221</v>
       </c>
       <c r="O36" s="1">
-        <v>0.92486849999999998</v>
+        <v>0.87596739999999995</v>
       </c>
       <c r="P36" s="1">
-        <v>2.7535314999999998</v>
-      </c>
-      <c r="Q36" s="15">
-        <v>9.3050999999999995E-2</v>
+        <v>2.6755817</v>
+      </c>
+      <c r="Q36" s="13">
+        <v>0.13483000000000001</v>
       </c>
       <c r="S36" s="1">
-        <v>1.4876545999999999</v>
+        <v>1.4365333</v>
       </c>
       <c r="T36" s="1">
-        <v>0.8628188</v>
+        <v>0.82402750000000002</v>
       </c>
       <c r="U36" s="1">
-        <v>2.5649839000000001</v>
-      </c>
-      <c r="V36" s="15">
-        <v>0.15290000000000001</v>
+        <v>2.5043193000000001</v>
+      </c>
+      <c r="V36" s="13">
+        <v>0.20135900000000001</v>
       </c>
     </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.3">
@@ -1580,68 +1500,68 @@
         <v>5</v>
       </c>
       <c r="D37" s="1">
-        <v>1.6736162999999999</v>
+        <v>1.6567049</v>
       </c>
       <c r="E37" s="1">
-        <v>0.89635100000000001</v>
+        <v>0.87469929999999996</v>
       </c>
       <c r="F37" s="1">
-        <v>3.1248824000000002</v>
-      </c>
-      <c r="G37" s="15">
-        <v>0.10593</v>
+        <v>3.1378450999999998</v>
+      </c>
+      <c r="G37" s="13">
+        <v>0.121292</v>
       </c>
       <c r="I37" s="1">
-        <v>1.414412</v>
+        <v>1.4027189</v>
       </c>
       <c r="J37" s="1">
-        <v>0.76605199999999996</v>
+        <v>0.75055430000000001</v>
       </c>
       <c r="K37" s="1">
-        <v>2.6115214999999998</v>
-      </c>
-      <c r="L37" s="15">
-        <v>0.26762999999999998</v>
+        <v>2.6215563999999998</v>
+      </c>
+      <c r="L37" s="13">
+        <v>0.28872399999999998</v>
       </c>
       <c r="N37" s="1">
-        <v>1.7002641999999999</v>
+        <v>1.6444422999999999</v>
       </c>
       <c r="O37" s="1">
-        <v>0.91565560000000001</v>
+        <v>0.87258769999999997</v>
       </c>
       <c r="P37" s="1">
-        <v>3.1571896000000002</v>
-      </c>
-      <c r="Q37" s="15">
-        <v>9.2741000000000004E-2</v>
+        <v>3.0990473999999999</v>
+      </c>
+      <c r="Q37" s="13">
+        <v>0.12389</v>
       </c>
       <c r="S37" s="1">
-        <v>1.3839486000000001</v>
+        <v>1.3875995000000001</v>
       </c>
       <c r="T37" s="1">
-        <v>0.74723019999999996</v>
+        <v>0.73956270000000002</v>
       </c>
       <c r="U37" s="1">
-        <v>2.5632179000000002</v>
-      </c>
-      <c r="V37" s="15">
-        <v>0.30127999999999999</v>
+        <v>2.6034742999999998</v>
+      </c>
+      <c r="V37" s="13">
+        <v>0.30745800000000001</v>
       </c>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G38" s="15"/>
+      <c r="G38" s="13"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="15"/>
+      <c r="L38" s="13"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="15"/>
+      <c r="Q38" s="13"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
-      <c r="V38" s="15"/>
+      <c r="V38" s="13"/>
     </row>
     <row r="39" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
@@ -1653,103 +1573,103 @@
       <c r="D39" s="1">
         <v>1</v>
       </c>
-      <c r="E39" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="21"/>
-      <c r="G39" s="15"/>
+      <c r="E39" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="15"/>
+      <c r="G39" s="13"/>
       <c r="I39" s="1">
         <v>1</v>
       </c>
-      <c r="J39" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="K39" s="21"/>
-      <c r="L39" s="15"/>
+      <c r="J39" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K39" s="15"/>
+      <c r="L39" s="13"/>
       <c r="N39" s="1">
         <v>1</v>
       </c>
-      <c r="O39" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="P39" s="21"/>
-      <c r="Q39" s="15"/>
+      <c r="O39" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="13"/>
       <c r="S39" s="1">
         <v>1</v>
       </c>
-      <c r="T39" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="U39" s="21"/>
-      <c r="V39" s="15"/>
+      <c r="T39" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="U39" s="15"/>
+      <c r="V39" s="13"/>
     </row>
     <row r="40" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C40" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="1">
-        <v>0.7987474</v>
+        <v>0.78755319999999995</v>
       </c>
       <c r="E40" s="1">
-        <v>0.52503770000000005</v>
+        <v>0.5213932</v>
       </c>
       <c r="F40" s="1">
-        <v>1.2151457000000001</v>
-      </c>
-      <c r="G40" s="15">
-        <v>0.29322599999999999</v>
+        <v>1.1895821</v>
+      </c>
+      <c r="G40" s="13">
+        <v>0.25624400000000003</v>
       </c>
       <c r="I40" s="1">
-        <v>0.83604809999999996</v>
+        <v>0.82354450000000001</v>
       </c>
       <c r="J40" s="1">
-        <v>0.55096100000000003</v>
+        <v>0.54597180000000001</v>
       </c>
       <c r="K40" s="1">
-        <v>1.2686493999999999</v>
-      </c>
-      <c r="L40" s="15">
-        <v>0.39928999999999998</v>
+        <v>1.2422356000000001</v>
+      </c>
+      <c r="L40" s="13">
+        <v>0.35442200000000001</v>
       </c>
       <c r="N40" s="1">
-        <v>0.8457192</v>
+        <v>0.83438860000000004</v>
       </c>
       <c r="O40" s="1">
-        <v>0.55850679999999997</v>
+        <v>0.55276239999999999</v>
       </c>
       <c r="P40" s="1">
-        <v>1.2806306000000001</v>
-      </c>
-      <c r="Q40" s="15">
-        <v>0.42800500000000002</v>
+        <v>1.2595003</v>
+      </c>
+      <c r="Q40" s="13">
+        <v>0.3886</v>
       </c>
       <c r="S40" s="1">
-        <v>0.83966879999999999</v>
+        <v>0.83802359999999998</v>
       </c>
       <c r="T40" s="1">
-        <v>0.5525504</v>
+        <v>0.55439050000000001</v>
       </c>
       <c r="U40" s="1">
-        <v>1.2759809</v>
-      </c>
-      <c r="V40" s="15">
-        <v>0.41236</v>
+        <v>1.2667668000000001</v>
+      </c>
+      <c r="V40" s="13">
+        <v>0.40168599999999999</v>
       </c>
     </row>
     <row r="41" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G41" s="15"/>
+      <c r="G41" s="13"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="15"/>
+      <c r="L41" s="13"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="15"/>
+      <c r="Q41" s="13"/>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
-      <c r="V41" s="15"/>
+      <c r="V41" s="13"/>
     </row>
     <row r="42" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
@@ -1761,158 +1681,156 @@
       <c r="D42" s="1">
         <v>1</v>
       </c>
-      <c r="E42" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F42" s="21"/>
-      <c r="G42" s="15"/>
+      <c r="E42" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="15"/>
+      <c r="G42" s="13"/>
       <c r="I42" s="1">
         <v>1</v>
       </c>
-      <c r="J42" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="K42" s="21"/>
-      <c r="L42" s="15"/>
+      <c r="J42" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K42" s="15"/>
+      <c r="L42" s="13"/>
       <c r="N42" s="1">
         <v>1</v>
       </c>
-      <c r="O42" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="P42" s="21"/>
-      <c r="Q42" s="15"/>
+      <c r="O42" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="13"/>
       <c r="S42" s="1">
         <v>1</v>
       </c>
-      <c r="T42" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="U42" s="21"/>
-      <c r="V42" s="15"/>
+      <c r="T42" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="U42" s="15"/>
+      <c r="V42" s="13"/>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B43" s="22"/>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D43" s="1">
-        <v>1.3278782</v>
+        <v>1.2466625</v>
       </c>
       <c r="E43" s="1">
-        <v>0.55385470000000003</v>
+        <v>0.51670899999999997</v>
       </c>
       <c r="F43" s="1">
-        <v>3.1836159999999998</v>
-      </c>
-      <c r="G43" s="15">
-        <v>0.52489399999999997</v>
+        <v>3.0078197000000002</v>
+      </c>
+      <c r="G43" s="13">
+        <v>0.62356900000000004</v>
       </c>
       <c r="I43" s="1">
-        <v>1.2293894999999999</v>
+        <v>1.1690649</v>
       </c>
       <c r="J43" s="1">
-        <v>0.51435750000000002</v>
+        <v>0.48555959999999998</v>
       </c>
       <c r="K43" s="1">
-        <v>2.9384201000000001</v>
-      </c>
-      <c r="L43" s="15">
-        <v>0.64215999999999995</v>
+        <v>2.8147164</v>
+      </c>
+      <c r="L43" s="13">
+        <v>0.72741699999999998</v>
       </c>
       <c r="N43" s="1">
-        <v>1.2394982999999999</v>
+        <v>1.2144200000000001</v>
       </c>
       <c r="O43" s="1">
-        <v>0.51836099999999996</v>
+        <v>0.50352450000000004</v>
       </c>
       <c r="P43" s="1">
-        <v>2.9638730999999998</v>
-      </c>
-      <c r="Q43" s="15">
-        <v>0.629193</v>
+        <v>2.9289850999999998</v>
+      </c>
+      <c r="Q43" s="13">
+        <v>0.66527000000000003</v>
       </c>
       <c r="S43" s="1">
-        <v>1.1761983</v>
+        <v>1.1631521</v>
       </c>
       <c r="T43" s="1">
-        <v>0.4909616</v>
+        <v>0.4816569</v>
       </c>
       <c r="U43" s="1">
-        <v>2.8178223999999998</v>
-      </c>
-      <c r="V43" s="15">
-        <v>0.71572000000000002</v>
+        <v>2.8088931000000001</v>
+      </c>
+      <c r="V43" s="13">
+        <v>0.73679399999999995</v>
       </c>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B44" s="22"/>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D44" s="1">
-        <v>1.7442009999999999</v>
+        <v>1.7807580999999999</v>
       </c>
       <c r="E44" s="1">
-        <v>0.63120730000000003</v>
+        <v>0.63596330000000001</v>
       </c>
       <c r="F44" s="1">
-        <v>4.8197121000000003</v>
-      </c>
-      <c r="G44" s="15">
-        <v>0.28328300000000001</v>
+        <v>4.9862926999999999</v>
+      </c>
+      <c r="G44" s="13">
+        <v>0.27190199999999998</v>
       </c>
       <c r="I44" s="1">
-        <v>1.7860788000000001</v>
+        <v>1.8405617000000001</v>
       </c>
       <c r="J44" s="1">
-        <v>0.64846250000000005</v>
+        <v>0.65841950000000005</v>
       </c>
       <c r="K44" s="1">
-        <v>4.9194483</v>
-      </c>
-      <c r="L44" s="15">
-        <v>0.26173000000000002</v>
+        <v>5.1451503000000001</v>
+      </c>
+      <c r="L44" s="13">
+        <v>0.244645</v>
       </c>
       <c r="N44" s="1">
-        <v>1.8301921999999999</v>
+        <v>1.9414027</v>
       </c>
       <c r="O44" s="1">
-        <v>0.66308730000000005</v>
+        <v>0.69313089999999999</v>
       </c>
       <c r="P44" s="1">
-        <v>5.0515273000000001</v>
-      </c>
-      <c r="Q44" s="15">
-        <v>0.243174</v>
+        <v>5.4377095000000004</v>
+      </c>
+      <c r="Q44" s="13">
+        <v>0.20668</v>
       </c>
       <c r="S44" s="1">
-        <v>1.7209774</v>
+        <v>1.8427397000000001</v>
       </c>
       <c r="T44" s="1">
-        <v>0.62366960000000005</v>
+        <v>0.65900389999999998</v>
       </c>
       <c r="U44" s="1">
-        <v>4.7489298</v>
-      </c>
-      <c r="V44" s="15">
-        <v>0.29437999999999998</v>
+        <v>5.1527605000000003</v>
+      </c>
+      <c r="V44" s="13">
+        <v>0.243867</v>
       </c>
     </row>
     <row r="45" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G45" s="15"/>
+      <c r="G45" s="13"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="15"/>
+      <c r="L45" s="13"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
-      <c r="Q45" s="15"/>
+      <c r="Q45" s="13"/>
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
-      <c r="V45" s="15"/>
+      <c r="V45" s="13"/>
     </row>
     <row r="46" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
@@ -1924,106 +1842,106 @@
       <c r="D46" s="1">
         <v>1</v>
       </c>
-      <c r="E46" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F46" s="21"/>
-      <c r="G46" s="15"/>
+      <c r="E46" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" s="15"/>
+      <c r="G46" s="13"/>
       <c r="I46" s="1">
         <v>1</v>
       </c>
-      <c r="J46" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="K46" s="21"/>
-      <c r="L46" s="15"/>
+      <c r="J46" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K46" s="15"/>
+      <c r="L46" s="13"/>
       <c r="N46" s="1">
         <v>1</v>
       </c>
-      <c r="O46" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="P46" s="21"/>
-      <c r="Q46" s="15"/>
+      <c r="O46" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="P46" s="15"/>
+      <c r="Q46" s="13"/>
       <c r="S46" s="1">
         <v>1</v>
       </c>
-      <c r="T46" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="U46" s="21"/>
-      <c r="V46" s="15"/>
+      <c r="T46" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="U46" s="15"/>
+      <c r="V46" s="13"/>
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C47" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D47" s="12">
-        <v>2.0386867999999998</v>
+        <v>1.9269619</v>
       </c>
       <c r="E47" s="12">
-        <v>1.1972046000000001</v>
+        <v>1.1016668000000001</v>
       </c>
       <c r="F47" s="12">
-        <v>3.4716236999999999</v>
-      </c>
-      <c r="G47" s="17">
-        <v>8.7489999999999998E-3</v>
+        <v>3.3705129</v>
+      </c>
+      <c r="G47" s="14">
+        <v>2.1507999999999999E-2</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="12">
-        <v>2.0054085000000001</v>
+        <v>1.8840809000000001</v>
       </c>
       <c r="J47" s="12">
-        <v>1.1838652999999999</v>
+        <v>1.0796410999999999</v>
       </c>
       <c r="K47" s="12">
-        <v>3.3970615999999998</v>
-      </c>
-      <c r="L47" s="17">
-        <v>9.6900000000000007E-3</v>
+        <v>3.2879079999999998</v>
+      </c>
+      <c r="L47" s="14">
+        <v>2.5791999999999999E-2</v>
       </c>
       <c r="M47" s="3"/>
       <c r="N47" s="12">
-        <v>2.0297227000000002</v>
+        <v>1.9027004000000001</v>
       </c>
       <c r="O47" s="12">
-        <v>1.1965144000000001</v>
+        <v>1.0897810000000001</v>
       </c>
       <c r="P47" s="12">
-        <v>3.4431463999999998</v>
-      </c>
-      <c r="Q47" s="17">
-        <v>8.6800000000000002E-3</v>
+        <v>3.3220151000000002</v>
+      </c>
+      <c r="Q47" s="14">
+        <v>2.3699999999999999E-2</v>
       </c>
       <c r="R47" s="3"/>
       <c r="S47" s="12">
-        <v>2.0344087000000002</v>
+        <v>1.88792</v>
       </c>
       <c r="T47" s="12">
-        <v>1.2010641</v>
+        <v>1.0827977</v>
       </c>
       <c r="U47" s="12">
-        <v>3.4459599000000001</v>
-      </c>
-      <c r="V47" s="17">
-        <v>8.2799999999999992E-3</v>
+        <v>3.2916968999999998</v>
+      </c>
+      <c r="V47" s="14">
+        <v>2.5087999999999999E-2</v>
       </c>
     </row>
     <row r="48" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G48" s="15"/>
+      <c r="G48" s="13"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="15"/>
+      <c r="L48" s="13"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
-      <c r="Q48" s="15"/>
+      <c r="Q48" s="13"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
-      <c r="V48" s="15"/>
+      <c r="V48" s="13"/>
     </row>
     <row r="49" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
@@ -2035,96 +1953,204 @@
       <c r="D49" s="1">
         <v>1</v>
       </c>
-      <c r="E49" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F49" s="21"/>
-      <c r="G49" s="15"/>
+      <c r="E49" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49" s="15"/>
+      <c r="G49" s="13"/>
       <c r="I49" s="1">
         <v>1</v>
       </c>
-      <c r="J49" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="K49" s="21"/>
-      <c r="L49" s="15"/>
+      <c r="J49" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K49" s="15"/>
+      <c r="L49" s="13"/>
       <c r="N49" s="1">
         <v>1</v>
       </c>
-      <c r="O49" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="P49" s="21"/>
-      <c r="Q49" s="15"/>
+      <c r="O49" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="13"/>
       <c r="S49" s="1">
         <v>1</v>
       </c>
-      <c r="T49" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="U49" s="21"/>
-      <c r="V49" s="15"/>
-    </row>
-    <row r="50" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="4"/>
-      <c r="C50" s="4" t="s">
+      <c r="T49" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="U49" s="15"/>
+      <c r="V49" s="13"/>
+    </row>
+    <row r="50" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C50" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D50" s="13">
-        <v>1.7785441</v>
-      </c>
-      <c r="E50" s="13">
-        <v>0.96265699999999998</v>
-      </c>
-      <c r="F50" s="13">
-        <v>3.2859254999999998</v>
-      </c>
-      <c r="G50" s="16">
-        <v>6.5964999999999996E-2</v>
-      </c>
-      <c r="H50" s="14"/>
-      <c r="I50" s="10">
-        <v>1.8731608</v>
-      </c>
-      <c r="J50" s="10">
-        <v>1.0188372999999999</v>
-      </c>
-      <c r="K50" s="10">
-        <v>3.4438583</v>
-      </c>
-      <c r="L50" s="23">
-        <v>4.3389999999999998E-2</v>
-      </c>
-      <c r="M50" s="4"/>
-      <c r="N50" s="10">
-        <v>1.8499516</v>
-      </c>
-      <c r="O50" s="10">
-        <v>1.0014072000000001</v>
-      </c>
-      <c r="P50" s="10">
-        <v>3.4175114999999998</v>
-      </c>
-      <c r="Q50" s="23">
-        <v>4.9478000000000001E-2</v>
-      </c>
-      <c r="R50" s="4"/>
-      <c r="S50" s="10">
-        <v>1.8541255000000001</v>
-      </c>
-      <c r="T50" s="10">
-        <v>1.0051649</v>
-      </c>
-      <c r="U50" s="10">
-        <v>3.4201166000000001</v>
-      </c>
-      <c r="V50" s="23">
-        <v>4.811E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="D50" s="1">
+        <v>1.5748849</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0.84040400000000004</v>
+      </c>
+      <c r="F50" s="1">
+        <v>2.9512741</v>
+      </c>
+      <c r="G50" s="13">
+        <v>0.156276</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1.6313663</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0.87188580000000004</v>
+      </c>
+      <c r="K50" s="1">
+        <v>3.0524135000000001</v>
+      </c>
+      <c r="L50" s="13">
+        <v>0.12567200000000001</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1.6430909</v>
+      </c>
+      <c r="O50" s="1">
+        <v>0.87590579999999996</v>
+      </c>
+      <c r="P50" s="1">
+        <v>3.0822351000000001</v>
+      </c>
+      <c r="Q50" s="13">
+        <v>0.12175</v>
+      </c>
+      <c r="S50" s="1">
+        <v>1.6664207</v>
+      </c>
+      <c r="T50" s="1">
+        <v>0.89036899999999997</v>
+      </c>
+      <c r="U50" s="1">
+        <v>3.1188845000000001</v>
+      </c>
+      <c r="V50" s="13">
+        <v>0.11022800000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="G51" s="13"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="13"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="13"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="13"/>
+    </row>
+    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" s="15"/>
+      <c r="G52" s="13"/>
+      <c r="I52" s="1">
+        <v>1</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K52" s="15"/>
+      <c r="L52" s="13"/>
+      <c r="N52" s="1">
+        <v>1</v>
+      </c>
+      <c r="O52" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="P52" s="15"/>
+      <c r="Q52" s="13"/>
+      <c r="S52" s="1">
+        <v>1</v>
+      </c>
+      <c r="T52" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="U52" s="15"/>
+      <c r="V52" s="13"/>
+    </row>
+    <row r="53" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="4"/>
+      <c r="C53" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="10">
+        <v>2.9496329000000001</v>
+      </c>
+      <c r="E53" s="10">
+        <v>1.8380817</v>
+      </c>
+      <c r="F53" s="10">
+        <v>4.7333774999999996</v>
+      </c>
+      <c r="G53" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="10">
+        <v>3.0672202999999998</v>
+      </c>
+      <c r="J53" s="10">
+        <v>1.9178933</v>
+      </c>
+      <c r="K53" s="10">
+        <v>4.9052993000000003</v>
+      </c>
+      <c r="L53" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M53" s="4"/>
+      <c r="N53" s="10">
+        <v>3.0318578999999999</v>
+      </c>
+      <c r="O53" s="10">
+        <v>1.8972473999999999</v>
+      </c>
+      <c r="P53" s="10">
+        <v>4.8449992000000002</v>
+      </c>
+      <c r="Q53" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="R53" s="4"/>
+      <c r="S53" s="10">
+        <v>3.0550073000000002</v>
+      </c>
+      <c r="T53" s="10">
+        <v>1.9088738000000001</v>
+      </c>
+      <c r="U53" s="10">
+        <v>4.8893066999999997</v>
+      </c>
+      <c r="V53" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="36">
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="J49:K49"/>
     <mergeCell ref="O49:P49"/>
@@ -2137,13 +2163,6 @@
     <mergeCell ref="J46:K46"/>
     <mergeCell ref="O46:P46"/>
     <mergeCell ref="T46:U46"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="E12:F12"/>
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="T39:U39"/>
     <mergeCell ref="T26:U26"/>
@@ -2152,11 +2171,22 @@
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="O35:P35"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="O52:P52"/>
+    <mergeCell ref="T52:U52"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="I5:L5"/>
     <mergeCell ref="N5:Q5"/>
     <mergeCell ref="S5:V5"/>
     <mergeCell ref="O21:P21"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="E12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
